--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C71D82-C581-4E35-86C1-4B40180195DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAECBC9-CEC2-4170-95FB-6AE9EDF1FBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8537" uniqueCount="1510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8550" uniqueCount="1511">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4566,6 +4566,9 @@
   </si>
   <si>
     <t>04:18:00.0</t>
+  </si>
+  <si>
+    <t>Hornseeli</t>
   </si>
 </sst>
 </file>
@@ -5101,7 +5104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1494"/>
+  <dimension ref="A1:Y1496"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -42438,7 +42441,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1489" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1489" s="7" t="s">
         <v>51</v>
       </c>
@@ -42473,7 +42476,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1490" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1490" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1490" s="7" t="s">
         <v>1431</v>
       </c>
@@ -42496,7 +42499,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1491" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1491" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1491" s="7" t="s">
         <v>55</v>
       </c>
@@ -42516,7 +42519,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="1492" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1492" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1492" s="7" t="s">
         <v>51</v>
       </c>
@@ -42548,7 +42551,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1493" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1493" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1493" s="1" t="s">
         <v>55</v>
       </c>
@@ -42573,7 +42576,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="1494" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1494" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1494" s="1" t="s">
         <v>55</v>
       </c>
@@ -42598,6 +42601,61 @@
       </c>
       <c r="K1494" s="7" t="s">
         <v>1507</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1495" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1495" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1495" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1495" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="I1495" s="9" t="s">
+        <v>1510</v>
+      </c>
+      <c r="J1495" s="1">
+        <v>46278</v>
+      </c>
+      <c r="T1495" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="U1495" s="7" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1496" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1496" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1496" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="I1496" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="J1496" s="1">
+        <v>46279</v>
+      </c>
+      <c r="K1496" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="L1496" s="7">
+        <v>632</v>
+      </c>
+      <c r="N1496" s="7">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="P1496" s="7" t="s">
+        <v>1075</v>
       </c>
     </row>
   </sheetData>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAECBC9-CEC2-4170-95FB-6AE9EDF1FBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9C872B-EB33-41D6-88AB-A140E64E0B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8550" uniqueCount="1511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8566" uniqueCount="1514">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4569,6 +4569,15 @@
   </si>
   <si>
     <t>Hornseeli</t>
+  </si>
+  <si>
+    <t>00:28:33.8</t>
+  </si>
+  <si>
+    <t>00:39:16.1</t>
+  </si>
+  <si>
+    <t>00:28:03.1</t>
   </si>
 </sst>
 </file>
@@ -5104,7 +5113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1496"/>
+  <dimension ref="A1:Y1499"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -42658,6 +42667,81 @@
         <v>1075</v>
       </c>
     </row>
+    <row r="1497" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1497" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1497" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="C1497" s="9" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J1497" s="1">
+        <v>46280</v>
+      </c>
+      <c r="K1497" s="7" t="s">
+        <v>1511</v>
+      </c>
+      <c r="L1497" s="7">
+        <v>1020</v>
+      </c>
+      <c r="T1497" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1498" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1498" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="C1498" s="9" t="s">
+        <v>1058</v>
+      </c>
+      <c r="J1498" s="1">
+        <v>46281</v>
+      </c>
+      <c r="K1498" s="7" t="s">
+        <v>1512</v>
+      </c>
+      <c r="L1498" s="7">
+        <v>28</v>
+      </c>
+      <c r="M1498" s="7">
+        <v>28</v>
+      </c>
+      <c r="N1498" s="7">
+        <v>6.4</v>
+      </c>
+      <c r="P1498" s="7" t="s">
+        <v>949</v>
+      </c>
+      <c r="T1498" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1499" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1499" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1499" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1499" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="J1499" s="1">
+        <v>46282</v>
+      </c>
+      <c r="K1499" s="7" t="s">
+        <v>1513</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y1494">
     <sortCondition ref="J2:J1494"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9C872B-EB33-41D6-88AB-A140E64E0B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABBBEEC-0238-4720-9953-AFFB918AF299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8566" uniqueCount="1514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8583" uniqueCount="1516">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4578,6 +4578,12 @@
   </si>
   <si>
     <t>00:28:03.1</t>
+  </si>
+  <si>
+    <t>00:31:30.8</t>
+  </si>
+  <si>
+    <t>00:49:30.3</t>
   </si>
 </sst>
 </file>
@@ -5113,7 +5119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1499"/>
+  <dimension ref="A1:Y1502"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -42742,6 +42748,90 @@
         <v>1513</v>
       </c>
     </row>
+    <row r="1500" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1500" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1500" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1500" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1500" s="9" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I1500" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="J1500" s="1">
+        <v>46284</v>
+      </c>
+      <c r="L1500" s="7">
+        <v>475</v>
+      </c>
+      <c r="M1500" s="7">
+        <v>22</v>
+      </c>
+      <c r="N1500" s="7">
+        <v>4.25</v>
+      </c>
+      <c r="P1500" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1501" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1501" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1501" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1501" s="2"/>
+      <c r="E1501" s="2"/>
+      <c r="F1501" s="2"/>
+      <c r="G1501" s="2"/>
+      <c r="H1501" s="2"/>
+      <c r="I1501" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1501" s="1">
+        <v>46285</v>
+      </c>
+      <c r="K1501" s="7" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1502" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1502" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1502" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1502" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E1502" s="2"/>
+      <c r="F1502" s="2"/>
+      <c r="G1502" s="2"/>
+      <c r="H1502" s="2"/>
+      <c r="I1502" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="J1502" s="1">
+        <v>46285</v>
+      </c>
+      <c r="K1502" s="7" t="s">
+        <v>1515</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y1494">
     <sortCondition ref="J2:J1494"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABBBEEC-0238-4720-9953-AFFB918AF299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8742971-9001-45CC-8E51-A8748B9477B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8583" uniqueCount="1516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8604" uniqueCount="1522">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4584,6 +4584,24 @@
   </si>
   <si>
     <t>00:49:30.3</t>
+  </si>
+  <si>
+    <t>00:25:51.1</t>
+  </si>
+  <si>
+    <t>01:05:04.0</t>
+  </si>
+  <si>
+    <t>01:43:35.1</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>Bachalpsee</t>
+  </si>
+  <si>
+    <t>02:25:58.3</t>
   </si>
 </sst>
 </file>
@@ -5119,7 +5137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1502"/>
+  <dimension ref="A1:Y1515"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -42832,6 +42850,110 @@
         <v>1515</v>
       </c>
     </row>
+    <row r="1503" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1503" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1503" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1503" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1503" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1503" s="1">
+        <v>46287</v>
+      </c>
+      <c r="K1503" s="7" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1504" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1504" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1504" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1504" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1504" s="1">
+        <v>46287</v>
+      </c>
+      <c r="K1504" s="7" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1505" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1505" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1505" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1505" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1505" s="1">
+        <v>46287</v>
+      </c>
+      <c r="K1505" s="7" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1506" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1506" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1506" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1506" s="9" t="s">
+        <v>1519</v>
+      </c>
+      <c r="J1506" s="1">
+        <v>46287</v>
+      </c>
+      <c r="K1506" s="7" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I1507" s="9" t="s">
+        <v>1520</v>
+      </c>
+      <c r="J1507" s="1">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1513" s="1"/>
+      <c r="B1513" s="1"/>
+      <c r="J1513" s="1"/>
+    </row>
+    <row r="1514" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1514" s="1"/>
+      <c r="B1514" s="1"/>
+      <c r="J1514" s="1"/>
+    </row>
+    <row r="1515" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1515" s="1"/>
+      <c r="B1515" s="1"/>
+      <c r="I1515" s="2"/>
+      <c r="J1515" s="1"/>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y1494">
     <sortCondition ref="J2:J1494"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8742971-9001-45CC-8E51-A8748B9477B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E6A008-C17E-4910-839A-2B347D8C3E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8604" uniqueCount="1522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8628" uniqueCount="1525">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4448,12 +4448,6 @@
     <t>00:30:16.6</t>
   </si>
   <si>
-    <t>00:29:10.0</t>
-  </si>
-  <si>
-    <t>00:48:27.7</t>
-  </si>
-  <si>
     <t>00:29:35.3</t>
   </si>
   <si>
@@ -4602,6 +4596,21 @@
   </si>
   <si>
     <t>02:25:58.3</t>
+  </si>
+  <si>
+    <t>00:44:03.7</t>
+  </si>
+  <si>
+    <t>00:28:54.3</t>
+  </si>
+  <si>
+    <t>00:29:32.9</t>
+  </si>
+  <si>
+    <t>00:48:30.7</t>
+  </si>
+  <si>
+    <t>00:46:21.3</t>
   </si>
 </sst>
 </file>
@@ -10254,7 +10263,7 @@
         <v>43729</v>
       </c>
       <c r="K193" s="7" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="194" spans="1:25" x14ac:dyDescent="0.25">
@@ -10277,7 +10286,7 @@
         <v>43729</v>
       </c>
       <c r="K194" s="7" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="195" spans="1:25" x14ac:dyDescent="0.25">
@@ -10380,7 +10389,7 @@
         <v>43743</v>
       </c>
       <c r="K198" s="7" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="199" spans="1:25" x14ac:dyDescent="0.25">
@@ -13212,7 +13221,7 @@
         <v>44113</v>
       </c>
       <c r="K309" s="7" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="310" spans="1:19" x14ac:dyDescent="0.25">
@@ -34413,7 +34422,7 @@
         <v>45887</v>
       </c>
       <c r="K1195" s="7" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="1196" spans="1:16" x14ac:dyDescent="0.25">
@@ -40388,7 +40397,7 @@
         <v>486</v>
       </c>
       <c r="I1413" s="9" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="J1413" s="1">
         <v>46192</v>
@@ -41757,7 +41766,7 @@
         <v>46244</v>
       </c>
       <c r="K1463" s="7" t="s">
-        <v>1470</v>
+        <v>864</v>
       </c>
     </row>
     <row r="1464" spans="1:22" x14ac:dyDescent="0.25">
@@ -41784,7 +41793,7 @@
         <v>46244</v>
       </c>
       <c r="K1464" s="7" t="s">
-        <v>1471</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="1465" spans="1:22" x14ac:dyDescent="0.25">
@@ -41804,7 +41813,7 @@
         <v>46245</v>
       </c>
       <c r="K1465" s="7" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="P1465" s="7" t="s">
         <v>1051</v>
@@ -41830,7 +41839,7 @@
         <v>46245</v>
       </c>
       <c r="K1466" s="7" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="P1466" s="7" t="s">
         <v>1051</v>
@@ -41856,7 +41865,7 @@
         <v>46245</v>
       </c>
       <c r="K1467" s="7" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="L1467" s="7">
         <v>814</v>
@@ -41882,7 +41891,7 @@
         <v>788</v>
       </c>
       <c r="D1468" s="9" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="E1468" s="9" t="s">
         <v>900</v>
@@ -41928,7 +41937,7 @@
         <v>46248</v>
       </c>
       <c r="K1469" s="7" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="1470" spans="1:22" x14ac:dyDescent="0.25">
@@ -41953,7 +41962,7 @@
         <v>46248</v>
       </c>
       <c r="K1470" s="7" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="1471" spans="1:22" x14ac:dyDescent="0.25">
@@ -41982,7 +41991,7 @@
         <v>46248</v>
       </c>
       <c r="K1471" s="7" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="1472" spans="1:22" x14ac:dyDescent="0.25">
@@ -41996,7 +42005,7 @@
         <v>933</v>
       </c>
       <c r="I1472" s="9" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="J1472" s="1">
         <v>46249</v>
@@ -42031,7 +42040,7 @@
         <v>46252</v>
       </c>
       <c r="K1473" s="7" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="L1473" s="7">
         <v>247</v>
@@ -42063,7 +42072,7 @@
         <v>46256</v>
       </c>
       <c r="K1474" s="7" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="L1474" s="7">
         <v>361</v>
@@ -42095,7 +42104,7 @@
         <v>46256</v>
       </c>
       <c r="K1475" s="7" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="L1475" s="7">
         <v>853</v>
@@ -42127,7 +42136,7 @@
         <v>46257</v>
       </c>
       <c r="K1476" s="7" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1477" spans="1:20" x14ac:dyDescent="0.25">
@@ -42150,7 +42159,7 @@
         <v>46257</v>
       </c>
       <c r="K1477" s="7" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1478" spans="1:20" x14ac:dyDescent="0.25">
@@ -42167,7 +42176,7 @@
         <v>46259</v>
       </c>
       <c r="K1478" s="7" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="L1478" s="7">
         <v>1061</v>
@@ -42190,7 +42199,7 @@
         <v>46260</v>
       </c>
       <c r="K1479" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="L1479" s="7">
         <v>1106</v>
@@ -42219,7 +42228,7 @@
         <v>46261</v>
       </c>
       <c r="K1480" s="7" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="L1480" s="7">
         <v>456</v>
@@ -42256,7 +42265,7 @@
         <v>46262</v>
       </c>
       <c r="K1481" s="7" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1482" spans="1:20" x14ac:dyDescent="0.25">
@@ -42273,7 +42282,7 @@
         <v>46264</v>
       </c>
       <c r="K1482" s="7" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="L1482" s="7">
         <v>546</v>
@@ -42302,7 +42311,7 @@
         <v>46266</v>
       </c>
       <c r="K1483" s="7" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="L1483" s="7">
         <v>1219</v>
@@ -42325,7 +42334,7 @@
         <v>46267</v>
       </c>
       <c r="K1484" s="7" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="L1484" s="7">
         <v>132</v>
@@ -42357,13 +42366,13 @@
         <v>486</v>
       </c>
       <c r="I1485" s="9" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="J1485" s="1">
         <v>46268</v>
       </c>
       <c r="K1485" s="7" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="L1485" s="7">
         <v>24</v>
@@ -42401,7 +42410,7 @@
         <v>46268</v>
       </c>
       <c r="K1486" s="7" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="L1486" s="7">
         <v>468</v>
@@ -42439,7 +42448,7 @@
         <v>46269</v>
       </c>
       <c r="K1487" s="7" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1488" spans="1:20" x14ac:dyDescent="0.25">
@@ -42450,16 +42459,16 @@
         <v>56</v>
       </c>
       <c r="C1488" s="9" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="I1488" s="9" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="J1488" s="1">
         <v>46270</v>
       </c>
       <c r="K1488" s="7" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="L1488" s="7">
         <v>719</v>
@@ -42482,19 +42491,19 @@
         <v>56</v>
       </c>
       <c r="C1489" s="9" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="D1489" s="9" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="I1489" s="9" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="J1489" s="1">
         <v>46270</v>
       </c>
       <c r="K1489" s="7" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="L1489" s="7">
         <v>1000</v>
@@ -42523,7 +42532,7 @@
         <v>46271</v>
       </c>
       <c r="K1490" s="7" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="L1490" s="7">
         <v>1307</v>
@@ -42549,7 +42558,7 @@
         <v>46273</v>
       </c>
       <c r="K1491" s="7" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="1492" spans="1:21" x14ac:dyDescent="0.25">
@@ -42569,7 +42578,7 @@
         <v>46275</v>
       </c>
       <c r="K1492" s="7" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="L1492" s="7">
         <v>552</v>
@@ -42606,7 +42615,7 @@
         <v>46276</v>
       </c>
       <c r="K1493" s="7" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="1494" spans="1:21" x14ac:dyDescent="0.25">
@@ -42633,7 +42642,7 @@
         <v>46276</v>
       </c>
       <c r="K1494" s="7" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="1495" spans="1:21" x14ac:dyDescent="0.25">
@@ -42650,7 +42659,7 @@
         <v>850</v>
       </c>
       <c r="I1495" s="9" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="J1495" s="1">
         <v>46278</v>
@@ -42705,7 +42714,7 @@
         <v>46280</v>
       </c>
       <c r="K1497" s="7" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="L1497" s="7">
         <v>1020</v>
@@ -42728,7 +42737,7 @@
         <v>46281</v>
       </c>
       <c r="K1498" s="7" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="L1498" s="7">
         <v>28</v>
@@ -42763,7 +42772,7 @@
         <v>46282</v>
       </c>
       <c r="K1499" s="7" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="1500" spans="1:21" x14ac:dyDescent="0.25">
@@ -42820,7 +42829,7 @@
         <v>46285</v>
       </c>
       <c r="K1501" s="7" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="1502" spans="1:21" x14ac:dyDescent="0.25">
@@ -42847,7 +42856,7 @@
         <v>46285</v>
       </c>
       <c r="K1502" s="7" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="1503" spans="1:21" x14ac:dyDescent="0.25">
@@ -42867,7 +42876,7 @@
         <v>46287</v>
       </c>
       <c r="K1503" s="7" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="1504" spans="1:21" x14ac:dyDescent="0.25">
@@ -42887,10 +42896,10 @@
         <v>46287</v>
       </c>
       <c r="K1504" s="7" t="s">
-        <v>1517</v>
-      </c>
-    </row>
-    <row r="1505" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1505" s="1" t="s">
         <v>55</v>
       </c>
@@ -42907,10 +42916,10 @@
         <v>46287</v>
       </c>
       <c r="K1505" s="7" t="s">
-        <v>1518</v>
-      </c>
-    </row>
-    <row r="1506" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1506" s="1" t="s">
         <v>55</v>
       </c>
@@ -42921,34 +42930,148 @@
         <v>24</v>
       </c>
       <c r="I1506" s="9" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="J1506" s="1">
         <v>46287</v>
       </c>
       <c r="K1506" s="7" t="s">
-        <v>1521</v>
-      </c>
-    </row>
-    <row r="1507" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1507" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1507" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1507" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="I1507" s="9" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="J1507" s="1">
         <v>46287</v>
       </c>
     </row>
-    <row r="1513" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1508" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1508" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1508" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="C1508" s="9" t="s">
+        <v>1058</v>
+      </c>
+      <c r="J1508" s="1">
+        <v>46288</v>
+      </c>
+      <c r="K1508" s="7" t="s">
+        <v>1520</v>
+      </c>
+      <c r="L1508" s="7">
+        <v>72</v>
+      </c>
+      <c r="M1508" s="7">
+        <v>67</v>
+      </c>
+      <c r="N1508" s="7">
+        <v>7.53</v>
+      </c>
+      <c r="P1508" s="7" t="s">
+        <v>949</v>
+      </c>
+      <c r="T1508" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1509" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1509" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="C1509" s="9" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J1509" s="1">
+        <v>46289</v>
+      </c>
+      <c r="K1509" s="7" t="s">
+        <v>1521</v>
+      </c>
+      <c r="L1509" s="7">
+        <v>1003</v>
+      </c>
+      <c r="T1509" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1510" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1510" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1510" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1510" s="2"/>
+      <c r="E1510" s="2"/>
+      <c r="F1510" s="2"/>
+      <c r="G1510" s="2"/>
+      <c r="H1510" s="2"/>
+      <c r="I1510" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1510" s="1">
+        <v>46290</v>
+      </c>
+      <c r="K1510" s="7" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1511" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1511" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1511" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1511" s="2"/>
+      <c r="E1511" s="2"/>
+      <c r="F1511" s="2"/>
+      <c r="G1511" s="2"/>
+      <c r="H1511" s="2"/>
+      <c r="I1511" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J1511" s="1">
+        <v>46290</v>
+      </c>
+      <c r="K1511" s="7" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1513" s="1"/>
       <c r="B1513" s="1"/>
       <c r="J1513" s="1"/>
     </row>
-    <row r="1514" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1514" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1514" s="1"/>
       <c r="B1514" s="1"/>
       <c r="J1514" s="1"/>
     </row>
-    <row r="1515" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1515" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1515" s="1"/>
       <c r="B1515" s="1"/>
       <c r="I1515" s="2"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E6A008-C17E-4910-839A-2B347D8C3E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9790A152-59D8-4291-8F95-EB4EB1FE684E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8628" uniqueCount="1525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8635" uniqueCount="1527">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4611,6 +4611,12 @@
   </si>
   <si>
     <t>00:46:21.3</t>
+  </si>
+  <si>
+    <t>3:15 abgezählt um vergleichbar zu sein mit 2025 Tour</t>
+  </si>
+  <si>
+    <t>01:39:43.0</t>
   </si>
 </sst>
 </file>
@@ -42899,7 +42905,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="1505" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1505" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1505" s="1" t="s">
         <v>55</v>
       </c>
@@ -42919,7 +42925,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="1506" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1506" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1506" s="1" t="s">
         <v>55</v>
       </c>
@@ -42939,7 +42945,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="1507" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1507" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1507" s="1" t="s">
         <v>55</v>
       </c>
@@ -42956,7 +42962,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="1508" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1508" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1508" s="7" t="s">
         <v>51</v>
       </c>
@@ -42988,7 +42994,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1509" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1509" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1509" s="7" t="s">
         <v>1431</v>
       </c>
@@ -43011,7 +43017,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1510" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1510" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1510" s="7" t="s">
         <v>55</v>
       </c>
@@ -43036,7 +43042,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="1511" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1511" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1511" s="7" t="s">
         <v>55</v>
       </c>
@@ -43061,17 +43067,43 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="1513" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1512" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A1512" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1512" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1512" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="D1512" s="9" t="s">
+        <v>1204</v>
+      </c>
+      <c r="I1512" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1512" s="1">
+        <v>46291</v>
+      </c>
+      <c r="K1512" s="7" t="s">
+        <v>1526</v>
+      </c>
+      <c r="Y1512" s="9" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1513" s="1"/>
       <c r="B1513" s="1"/>
       <c r="J1513" s="1"/>
     </row>
-    <row r="1514" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1514" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1514" s="1"/>
       <c r="B1514" s="1"/>
       <c r="J1514" s="1"/>
     </row>
-    <row r="1515" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1515" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1515" s="1"/>
       <c r="B1515" s="1"/>
       <c r="I1515" s="2"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9790A152-59D8-4291-8F95-EB4EB1FE684E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3548F35-AE14-4F8E-B871-3B73C569BB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="all" sheetId="7" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Y$1494</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Y$1515</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8635" uniqueCount="1527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8662" uniqueCount="1533">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4617,6 +4617,24 @@
   </si>
   <si>
     <t>01:39:43.0</t>
+  </si>
+  <si>
+    <t>00:54:39.3</t>
+  </si>
+  <si>
+    <t>00:30:13.9</t>
+  </si>
+  <si>
+    <t>00:39:06.0</t>
+  </si>
+  <si>
+    <t>Niederhorn</t>
+  </si>
+  <si>
+    <t>Vorsass</t>
+  </si>
+  <si>
+    <t>Merrrell</t>
   </si>
 </sst>
 </file>
@@ -5152,7 +5170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1515"/>
+  <dimension ref="A1:Y1516"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -43094,20 +43112,135 @@
       </c>
     </row>
     <row r="1513" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1513" s="1"/>
-      <c r="B1513" s="1"/>
-      <c r="J1513" s="1"/>
+      <c r="A1513" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1513" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="C1513" s="9" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J1513" s="1">
+        <v>46292</v>
+      </c>
+      <c r="K1513" s="7" t="s">
+        <v>1528</v>
+      </c>
+      <c r="L1513" s="7">
+        <v>1000</v>
+      </c>
+      <c r="T1513" s="7" t="s">
+        <v>1059</v>
+      </c>
     </row>
     <row r="1514" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1514" s="1"/>
-      <c r="B1514" s="1"/>
-      <c r="J1514" s="1"/>
+      <c r="A1514" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1514" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1514" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1514" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="I1514" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="J1514" s="1">
+        <v>46297</v>
+      </c>
+      <c r="K1514" s="7" t="s">
+        <v>1529</v>
+      </c>
+      <c r="L1514" s="7">
+        <v>469</v>
+      </c>
+      <c r="M1514" s="7">
+        <v>3</v>
+      </c>
+      <c r="N1514" s="7">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="P1514" s="7" t="s">
+        <v>1051</v>
+      </c>
     </row>
     <row r="1515" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1515" s="1"/>
-      <c r="B1515" s="1"/>
-      <c r="I1515" s="2"/>
-      <c r="J1515" s="1"/>
+      <c r="A1515" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1515" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1515" s="9" t="s">
+        <v>1530</v>
+      </c>
+      <c r="I1515" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="J1515" s="1">
+        <v>46298</v>
+      </c>
+      <c r="L1515" s="7">
+        <v>93</v>
+      </c>
+      <c r="M1515" s="7">
+        <v>429</v>
+      </c>
+      <c r="N1515" s="7">
+        <v>5.36</v>
+      </c>
+      <c r="P1515" s="7" t="s">
+        <v>1532</v>
+      </c>
+      <c r="T1515" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="U1515" s="7" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A1516" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1516" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1516" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="I1516" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1516" s="1">
+        <v>46299</v>
+      </c>
+      <c r="K1516" s="7" t="s">
+        <v>1527</v>
+      </c>
+      <c r="L1516" s="7">
+        <v>823</v>
+      </c>
+      <c r="M1516" s="7">
+        <v>0</v>
+      </c>
+      <c r="N1516" s="7">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="P1516" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="T1516" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="U1516" s="7" t="s">
+        <v>369</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y1494">

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3548F35-AE14-4F8E-B871-3B73C569BB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF9BFF5-F756-455D-9E61-4837CAB6EAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8662" uniqueCount="1533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8673" uniqueCount="1535">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4635,6 +4635,12 @@
   </si>
   <si>
     <t>Merrrell</t>
+  </si>
+  <si>
+    <t>00:28:15.4</t>
+  </si>
+  <si>
+    <t>00:51:53.2</t>
   </si>
 </sst>
 </file>
@@ -5170,7 +5176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1516"/>
+  <dimension ref="A1:Y1518"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -43242,6 +43248,58 @@
         <v>369</v>
       </c>
     </row>
+    <row r="1517" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A1517" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1517" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1517" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1517" s="2"/>
+      <c r="E1517" s="2"/>
+      <c r="F1517" s="2"/>
+      <c r="G1517" s="2"/>
+      <c r="H1517" s="2"/>
+      <c r="I1517" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="J1517" s="1">
+        <v>46300</v>
+      </c>
+      <c r="K1517" s="7" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A1518" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1518" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1518" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1518" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1518" s="2"/>
+      <c r="F1518" s="2"/>
+      <c r="G1518" s="2"/>
+      <c r="H1518" s="2"/>
+      <c r="I1518" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="J1518" s="1">
+        <v>46300</v>
+      </c>
+      <c r="K1518" s="7" t="s">
+        <v>1534</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y1494">
     <sortCondition ref="J2:J1494"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF9BFF5-F756-455D-9E61-4837CAB6EAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937B73B6-1B18-4A88-8773-5B6EAFD1B5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8673" uniqueCount="1535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8691" uniqueCount="1538">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4641,6 +4641,15 @@
   </si>
   <si>
     <t>00:51:53.2</t>
+  </si>
+  <si>
+    <t>00:30:43.5</t>
+  </si>
+  <si>
+    <t>01:05:44.2</t>
+  </si>
+  <si>
+    <t>01:28:19.9</t>
   </si>
 </sst>
 </file>
@@ -5176,7 +5185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1518"/>
+  <dimension ref="A1:Y1521"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -43300,6 +43309,87 @@
         <v>1534</v>
       </c>
     </row>
+    <row r="1519" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A1519" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1519" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1519" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1519" s="2"/>
+      <c r="E1519" s="2"/>
+      <c r="F1519" s="2"/>
+      <c r="G1519" s="2"/>
+      <c r="H1519" s="2"/>
+      <c r="I1519" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1519" s="1">
+        <v>46301</v>
+      </c>
+      <c r="K1519" s="7" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A1520" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1520" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1520" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1520" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E1520" s="2"/>
+      <c r="F1520" s="2"/>
+      <c r="G1520" s="2"/>
+      <c r="H1520" s="2"/>
+      <c r="I1520" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="J1520" s="1">
+        <v>46301</v>
+      </c>
+      <c r="K1520" s="7" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1521" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1521" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1521" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1521" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E1521" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F1521" s="2"/>
+      <c r="G1521" s="2"/>
+      <c r="H1521" s="2"/>
+      <c r="I1521" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J1521" s="1">
+        <v>46301</v>
+      </c>
+      <c r="K1521" s="7" t="s">
+        <v>1537</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y1494">
     <sortCondition ref="J2:J1494"/>
